--- a/pcb/robot/usb-pd-module/USB_PD_Module-top-pos.xlsx
+++ b/pcb/robot/usb-pd-module/USB_PD_Module-top-pos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JHORDAN\FREELANCE\PROYECTOS\KICAD_USB_PD_MODULAR\Github\smartphone-robot-cad\pcb\robot\usb-pd-module\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63A42BB-D8B1-4760-82E1-1EDB801DAC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1436FCF5-A5FF-4748-BA62-35AC9CF2C79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="58">
   <si>
     <t>C45</t>
   </si>
@@ -199,9 +199,6 @@
   </si>
   <si>
     <t>J4</t>
-  </si>
-  <si>
-    <t>J9</t>
   </si>
 </sst>
 </file>
@@ -1084,7 +1081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1344,47 +1341,47 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="B16">
-        <v>0.1</v>
+        <v>-34.409999999999997</v>
       </c>
       <c r="C16">
-        <v>6.75</v>
+        <v>-2.2755000000000001</v>
       </c>
       <c r="D16" t="s">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17">
-        <v>-34.409999999999997</v>
+        <v>-30.45</v>
       </c>
       <c r="C17">
-        <v>-2.2755000000000001</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="D17" t="s">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18">
-        <v>-30.45</v>
+        <v>-28.95</v>
       </c>
       <c r="C18">
-        <v>-0.77500000000000002</v>
+        <v>-0.75</v>
       </c>
       <c r="D18" t="s">
         <v>1</v>
@@ -1395,13 +1392,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19">
-        <v>-28.95</v>
+        <v>11</v>
       </c>
       <c r="C19">
-        <v>-0.75</v>
+        <v>-3.74</v>
       </c>
       <c r="D19" t="s">
         <v>1</v>
@@ -1412,10 +1409,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20">
         <v>-3.74</v>
@@ -1429,27 +1426,27 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="C21">
-        <v>-3.74</v>
+        <v>4.95</v>
       </c>
       <c r="D21" t="s">
         <v>1</v>
       </c>
       <c r="E21">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22">
-        <v>5.2</v>
+        <v>6.7</v>
       </c>
       <c r="C22">
         <v>4.95</v>
@@ -1463,251 +1460,251 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23">
-        <v>6.7</v>
+        <v>8.1750000000000007</v>
       </c>
       <c r="C23">
-        <v>4.95</v>
+        <v>1.25</v>
       </c>
       <c r="D23" t="s">
         <v>1</v>
       </c>
       <c r="E23">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24">
-        <v>8.1750000000000007</v>
+        <v>15.5</v>
       </c>
       <c r="C24">
-        <v>1.25</v>
+        <v>-4.4249999999999998</v>
       </c>
       <c r="D24" t="s">
         <v>1</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25">
-        <v>15.5</v>
+        <v>8.1750000000000007</v>
       </c>
       <c r="C25">
-        <v>-4.4249999999999998</v>
+        <v>-0.25</v>
       </c>
       <c r="D25" t="s">
         <v>1</v>
       </c>
       <c r="E25">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26">
-        <v>8.1750000000000007</v>
+        <v>17</v>
       </c>
       <c r="C26">
-        <v>-0.25</v>
+        <v>-4.4249999999999998</v>
       </c>
       <c r="D26" t="s">
         <v>1</v>
       </c>
       <c r="E26">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27">
-        <v>17</v>
+        <v>8.1750000000000007</v>
       </c>
       <c r="C27">
-        <v>-4.4249999999999998</v>
+        <v>-1.75</v>
       </c>
       <c r="D27" t="s">
         <v>1</v>
       </c>
       <c r="E27">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28">
-        <v>8.1750000000000007</v>
+        <v>-33.6</v>
       </c>
       <c r="C28">
-        <v>-1.75</v>
+        <v>4.5</v>
       </c>
       <c r="D28" t="s">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29">
-        <v>-33.6</v>
+        <v>-11.074999999999999</v>
       </c>
       <c r="C29">
-        <v>4.5</v>
+        <v>1.05</v>
       </c>
       <c r="D29" t="s">
         <v>1</v>
       </c>
       <c r="E29">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B30">
-        <v>-11.074999999999999</v>
+        <v>-8.5</v>
       </c>
       <c r="C30">
-        <v>1.05</v>
+        <v>-0.75</v>
       </c>
       <c r="D30" t="s">
         <v>1</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31">
-        <v>-8.5</v>
+        <v>-12.612500000000001</v>
       </c>
       <c r="C31">
-        <v>-0.75</v>
+        <v>-4.25</v>
       </c>
       <c r="D31" t="s">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32">
-        <v>-12.612500000000001</v>
+        <v>-27.5</v>
       </c>
       <c r="C32">
-        <v>-4.25</v>
+        <v>3.75</v>
       </c>
       <c r="D32" t="s">
         <v>1</v>
       </c>
       <c r="E32">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33">
-        <v>-27.5</v>
+        <v>-15.266342</v>
       </c>
       <c r="C33">
-        <v>3.75</v>
+        <v>-1.6685000000000001</v>
       </c>
       <c r="D33" t="s">
         <v>1</v>
       </c>
       <c r="E33">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B34">
-        <v>-15.266342</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="C34">
-        <v>-1.6685000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="D34" t="s">
         <v>1</v>
       </c>
       <c r="E34">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35">
-        <v>34.799999999999997</v>
+        <v>4.5</v>
       </c>
       <c r="C35">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="D35" t="s">
         <v>1</v>
       </c>
       <c r="E35">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B36">
-        <v>4.5</v>
+        <v>-3</v>
       </c>
       <c r="C36">
-        <v>1.75</v>
+        <v>-5.25</v>
       </c>
       <c r="D36" t="s">
         <v>1</v>
       </c>
       <c r="E36">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B37">
-        <v>-3</v>
+        <v>-11.5</v>
       </c>
       <c r="C37">
-        <v>-5.25</v>
+        <v>2.75</v>
       </c>
       <c r="D37" t="s">
         <v>1</v>
@@ -1718,47 +1715,47 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B38">
-        <v>-11.5</v>
+        <v>8</v>
       </c>
       <c r="C38">
-        <v>2.75</v>
+        <v>-4.25</v>
       </c>
       <c r="D38" t="s">
         <v>1</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B39">
-        <v>8</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="C39">
-        <v>-4.25</v>
+        <v>3.75</v>
       </c>
       <c r="D39" t="s">
         <v>1</v>
       </c>
       <c r="E39">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40">
-        <v>8.6999999999999993</v>
+        <v>36.1</v>
       </c>
       <c r="C40">
-        <v>3.75</v>
+        <v>-5.0999999999999996</v>
       </c>
       <c r="D40" t="s">
         <v>1</v>
@@ -1769,13 +1766,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B41">
-        <v>36.1</v>
+        <v>2.5</v>
       </c>
       <c r="C41">
-        <v>-5.0999999999999996</v>
+        <v>-5.25</v>
       </c>
       <c r="D41" t="s">
         <v>1</v>
@@ -1786,10 +1783,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B42">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="C42">
         <v>-5.25</v>
@@ -1803,13 +1800,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B43">
-        <v>5</v>
+        <v>33.35</v>
       </c>
       <c r="C43">
-        <v>-5.25</v>
+        <v>-5.0999999999999996</v>
       </c>
       <c r="D43" t="s">
         <v>1</v>
@@ -1820,13 +1817,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B44">
-        <v>33.35</v>
+        <v>12.75</v>
       </c>
       <c r="C44">
-        <v>-5.0999999999999996</v>
+        <v>0.25</v>
       </c>
       <c r="D44" t="s">
         <v>1</v>
@@ -1837,115 +1834,115 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B45">
-        <v>12.75</v>
+        <v>2.5</v>
       </c>
       <c r="C45">
-        <v>0.25</v>
+        <v>-3.75</v>
       </c>
       <c r="D45" t="s">
         <v>1</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B46">
-        <v>2.5</v>
+        <v>-11.1</v>
       </c>
       <c r="C46">
-        <v>-3.75</v>
+        <v>-1.5</v>
       </c>
       <c r="D46" t="s">
         <v>1</v>
       </c>
       <c r="E46">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B47">
-        <v>-11.1</v>
+        <v>-29.8</v>
       </c>
       <c r="C47">
-        <v>-1.5</v>
+        <v>-4.05</v>
       </c>
       <c r="D47" t="s">
         <v>1</v>
       </c>
       <c r="E47">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B48">
-        <v>-29.8</v>
+        <v>5</v>
       </c>
       <c r="C48">
-        <v>-4.05</v>
+        <v>-3.75</v>
       </c>
       <c r="D48" t="s">
         <v>1</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B49">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="C49">
-        <v>-3.75</v>
+        <v>-3.3</v>
       </c>
       <c r="D49" t="s">
         <v>1</v>
       </c>
       <c r="E49">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B50">
-        <v>6.1</v>
+        <v>-0.5</v>
       </c>
       <c r="C50">
-        <v>-3.3</v>
+        <v>3.1</v>
       </c>
       <c r="D50" t="s">
         <v>1</v>
       </c>
       <c r="E50">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B51">
-        <v>-0.5</v>
+        <v>-3.5</v>
       </c>
       <c r="C51">
-        <v>3.1</v>
+        <v>-3.75</v>
       </c>
       <c r="D51" t="s">
         <v>1</v>
@@ -1956,13 +1953,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B52">
-        <v>-3.5</v>
+        <v>0.5</v>
       </c>
       <c r="C52">
-        <v>-3.75</v>
+        <v>3.1</v>
       </c>
       <c r="D52" t="s">
         <v>1</v>
@@ -1973,35 +1970,18 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B53">
-        <v>0.5</v>
+        <v>-6.65</v>
       </c>
       <c r="C53">
-        <v>3.1</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="D53" t="s">
         <v>1</v>
       </c>
       <c r="E53">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" t="s">
-        <v>56</v>
-      </c>
-      <c r="B54">
-        <v>-6.65</v>
-      </c>
-      <c r="C54">
-        <v>2.2250000000000001</v>
-      </c>
-      <c r="D54" t="s">
-        <v>1</v>
-      </c>
-      <c r="E54">
         <v>-90</v>
       </c>
     </row>
